--- a/2024/validation/Table_1_data_afy_2024.xlsx
+++ b/2024/validation/Table_1_data_afy_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nmgov-my.sharepoint.com/personal/brad_wolaver_ose_nm_gov/Documents/Documents/_Projects/_APPs/RG/City_Santa_Fe/Buckman/Reporting/2024 Depletion Memo/TABLES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bradwolaver\projects\rg\santafe\2024\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{7A1F1533-AFE5-4BB6-AE23-E4E721244DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92083287-862B-4C43-B8A1-828B2FEB65EE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EBF8F2-59EB-470F-8253-96EFD41C6A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0F86D499-3F6C-4A61-950C-60785675ADA2}"/>
+    <workbookView xWindow="29535" yWindow="960" windowWidth="21600" windowHeight="12645" xr2:uid="{0F86D499-3F6C-4A61-950C-60785675ADA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1_data_afy_2024" sheetId="1" r:id="rId1"/>
@@ -188,7 +188,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,12 +371,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,7 +598,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -633,14 +627,11 @@
     <xf numFmtId="0" fontId="16" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2924,7 +2915,57 @@
         <v>1071.6166666666666</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="14"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
+    </row>
+    <row r="43" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="14"/>
+      <c r="O43" s="14"/>
+    </row>
     <row r="44" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>4</v>
@@ -2956,16 +2997,16 @@
       <c r="J44" s="2">
         <v>9</v>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="2">
         <v>10</v>
       </c>
-      <c r="L44" s="16">
+      <c r="L44" s="2">
         <v>11</v>
       </c>
-      <c r="M44" s="16">
-        <v>12</v>
-      </c>
-      <c r="N44" s="16">
+      <c r="M44" s="2">
+        <v>12</v>
+      </c>
+      <c r="N44" s="2">
         <v>13</v>
       </c>
       <c r="O44" s="2" t="s">
@@ -2973,7 +3014,7 @@
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B45" s="15">
@@ -3012,38 +3053,83 @@
         <f t="shared" si="2"/>
         <v>3.7876028844052739E-4</v>
       </c>
-      <c r="K45" s="17">
+      <c r="K45" s="15">
         <f t="shared" si="2"/>
         <v>0.11028479860150048</v>
       </c>
-      <c r="L45" s="17">
+      <c r="L45" s="15">
         <f t="shared" si="2"/>
         <v>9.920606016461506E-3</v>
       </c>
-      <c r="M45" s="17">
+      <c r="M45" s="15">
         <f t="shared" si="2"/>
         <v>7.1381746667637863E-3</v>
       </c>
-      <c r="N45" s="17">
+      <c r="N45" s="15">
         <f t="shared" si="2"/>
         <v>0.15443222375992427</v>
       </c>
-      <c r="O45" s="14">
+      <c r="O45" s="16">
         <f>SUM(B45:N45)</f>
         <v>1</v>
       </c>
     </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
+      <c r="O46" s="14"/>
+    </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="N47" s="18">
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="17">
         <f>SUM(K38:N38)</f>
         <v>386.85</v>
       </c>
+      <c r="O47" s="14"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="N48" s="19">
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
+      <c r="N48" s="18">
         <f>K45+L45+M45+N45</f>
         <v>0.28177580304465005</v>
       </c>
+      <c r="O48" s="14"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="T3:T38">
